--- a/jogos_2025-08-10.xlsx
+++ b/jogos_2025-08-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL210"/>
+  <dimension ref="A1:AL220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2168,10 +2168,10 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,58 +2390,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.43</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
       <c r="AB15" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="AL52" s="3" t="n">
-        <v>45879.40625</v>
+        <v>45879.39583333334</v>
       </c>
     </row>
     <row r="53">
@@ -7365,27 +7365,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="AL53" s="3" t="n">
-        <v>45879.41666666666</v>
+        <v>45879.40625</v>
       </c>
     </row>
     <row r="54">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8157,27 +8157,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="AL59" s="3" t="n">
-        <v>45879.4375</v>
+        <v>45879.41666666666</v>
       </c>
     </row>
     <row r="60">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8553,27 +8553,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="AL62" s="3" t="n">
-        <v>45879.45833333334</v>
+        <v>45879.4375</v>
       </c>
     </row>
     <row r="63">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12513,27 +12513,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12636,7 +12636,7 @@
         </is>
       </c>
       <c r="AL92" s="3" t="n">
-        <v>45879.47916666666</v>
+        <v>45879.45833333334</v>
       </c>
     </row>
     <row r="93">
@@ -12645,27 +12645,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="AL93" s="3" t="n">
-        <v>45879.47916666666</v>
+        <v>45879.45833333334</v>
       </c>
     </row>
     <row r="94">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,22 +13046,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13173,27 +13173,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13296,7 +13296,7 @@
         </is>
       </c>
       <c r="AL97" s="3" t="n">
-        <v>45879.48958333334</v>
+        <v>45879.47916666666</v>
       </c>
     </row>
     <row r="98">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="AL98" s="3" t="n">
-        <v>45879.48958333334</v>
+        <v>45879.47916666666</v>
       </c>
     </row>
     <row r="99">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="AL99" s="3" t="n">
-        <v>45879.5</v>
+        <v>45879.48958333334</v>
       </c>
     </row>
     <row r="100">
@@ -13569,12 +13569,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="AL100" s="3" t="n">
-        <v>45879.5</v>
+        <v>45879.48958333334</v>
       </c>
     </row>
     <row r="101">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13784,10 +13784,10 @@
         <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
         <v>0</v>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,22 +14234,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14318,10 +14318,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15026,22 +15026,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,22 +15950,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16473,12 +16473,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16596,7 +16596,7 @@
         </is>
       </c>
       <c r="AL122" s="3" t="n">
-        <v>45879.5</v>
+        <v>45879.52083333334</v>
       </c>
     </row>
     <row r="123">
@@ -16605,12 +16605,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="AL123" s="3" t="n">
-        <v>45879.5</v>
+        <v>45879.52083333334</v>
       </c>
     </row>
     <row r="124">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="AL124" s="3" t="n">
-        <v>45879.5</v>
+        <v>45879.52083333334</v>
       </c>
     </row>
     <row r="125">
@@ -16869,27 +16869,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16992,7 +16992,7 @@
         </is>
       </c>
       <c r="AL125" s="3" t="n">
-        <v>45879.5</v>
+        <v>45879.52083333334</v>
       </c>
     </row>
     <row r="126">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17534,22 +17534,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17661,27 +17661,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17784,7 +17784,7 @@
         </is>
       </c>
       <c r="AL131" s="3" t="n">
-        <v>45879.54166666666</v>
+        <v>45879.52083333334</v>
       </c>
     </row>
     <row r="132">
@@ -17793,12 +17793,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17916,7 +17916,7 @@
         </is>
       </c>
       <c r="AL132" s="3" t="n">
-        <v>45879.54166666666</v>
+        <v>45879.53125</v>
       </c>
     </row>
     <row r="133">
@@ -17925,12 +17925,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -18048,7 +18048,7 @@
         </is>
       </c>
       <c r="AL133" s="3" t="n">
-        <v>45879.54166666666</v>
+        <v>45879.53125</v>
       </c>
     </row>
     <row r="134">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18668,16 +18668,16 @@
         <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD138" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18986,22 +18986,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20342,13 +20342,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20834,22 +20834,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21440,16 +21440,16 @@
         <v>0</v>
       </c>
       <c r="Z159" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD159" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21621,27 +21621,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="AL161" s="3" t="n">
-        <v>45879.55208333334</v>
+        <v>45879.54166666666</v>
       </c>
     </row>
     <row r="162">
@@ -21753,12 +21753,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="AL162" s="3" t="n">
-        <v>45879.5625</v>
+        <v>45879.54166666666</v>
       </c>
     </row>
     <row r="163">
@@ -21885,27 +21885,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22008,7 +22008,7 @@
         </is>
       </c>
       <c r="AL163" s="3" t="n">
-        <v>45879.5625</v>
+        <v>45879.54166666666</v>
       </c>
     </row>
     <row r="164">
@@ -22017,12 +22017,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22140,7 +22140,7 @@
         </is>
       </c>
       <c r="AL164" s="3" t="n">
-        <v>45879.5625</v>
+        <v>45879.55208333334</v>
       </c>
     </row>
     <row r="165">
@@ -22281,27 +22281,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22404,7 +22404,7 @@
         </is>
       </c>
       <c r="AL166" s="3" t="n">
-        <v>45879.58333333334</v>
+        <v>45879.5625</v>
       </c>
     </row>
     <row r="167">
@@ -22413,27 +22413,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22536,7 +22536,7 @@
         </is>
       </c>
       <c r="AL167" s="3" t="n">
-        <v>45879.59375</v>
+        <v>45879.5625</v>
       </c>
     </row>
     <row r="168">
@@ -22545,12 +22545,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="AL168" s="3" t="n">
-        <v>45879.59375</v>
+        <v>45879.57291666666</v>
       </c>
     </row>
     <row r="169">
@@ -22677,12 +22677,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22766,10 +22766,10 @@
         <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD169" t="n">
         <v>0</v>
@@ -22800,7 +22800,7 @@
         </is>
       </c>
       <c r="AL169" s="3" t="n">
-        <v>45879.60416666666</v>
+        <v>45879.58333333334</v>
       </c>
     </row>
     <row r="170">
@@ -22809,12 +22809,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22932,7 +22932,7 @@
         </is>
       </c>
       <c r="AL170" s="3" t="n">
-        <v>45879.60416666666</v>
+        <v>45879.58333333334</v>
       </c>
     </row>
     <row r="171">
@@ -22941,27 +22941,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="AL171" s="3" t="n">
-        <v>45879.60416666666</v>
+        <v>45879.58333333334</v>
       </c>
     </row>
     <row r="172">
@@ -23073,27 +23073,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23196,7 +23196,7 @@
         </is>
       </c>
       <c r="AL172" s="3" t="n">
-        <v>45879.625</v>
+        <v>45879.58333333334</v>
       </c>
     </row>
     <row r="173">
@@ -23205,27 +23205,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AL173" s="3" t="n">
-        <v>45879.625</v>
+        <v>45879.59375</v>
       </c>
     </row>
     <row r="174">
@@ -23337,27 +23337,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="AL174" s="3" t="n">
-        <v>45879.625</v>
+        <v>45879.59375</v>
       </c>
     </row>
     <row r="175">
@@ -23469,27 +23469,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23510,13 +23510,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="AL175" s="3" t="n">
-        <v>45879.63541666666</v>
+        <v>45879.60416666666</v>
       </c>
     </row>
     <row r="176">
@@ -23601,12 +23601,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23724,7 +23724,7 @@
         </is>
       </c>
       <c r="AL176" s="3" t="n">
-        <v>45879.63541666666</v>
+        <v>45879.60416666666</v>
       </c>
     </row>
     <row r="177">
@@ -23733,12 +23733,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="AL177" s="3" t="n">
-        <v>45879.63541666666</v>
+        <v>45879.60416666666</v>
       </c>
     </row>
     <row r="178">
@@ -23865,27 +23865,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23906,13 +23906,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23954,10 +23954,10 @@
         <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC178" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD178" t="n">
         <v>0</v>
@@ -23988,7 +23988,7 @@
         </is>
       </c>
       <c r="AL178" s="3" t="n">
-        <v>45879.64583333334</v>
+        <v>45879.60416666666</v>
       </c>
     </row>
     <row r="179">
@@ -23997,12 +23997,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24120,7 +24120,7 @@
         </is>
       </c>
       <c r="AL179" s="3" t="n">
-        <v>45879.64583333334</v>
+        <v>45879.625</v>
       </c>
     </row>
     <row r="180">
@@ -24129,12 +24129,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24170,13 +24170,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="AL180" s="3" t="n">
-        <v>45879.64583333334</v>
+        <v>45879.625</v>
       </c>
     </row>
     <row r="181">
@@ -24261,27 +24261,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24384,7 +24384,7 @@
         </is>
       </c>
       <c r="AL181" s="3" t="n">
-        <v>45879.64583333334</v>
+        <v>45879.625</v>
       </c>
     </row>
     <row r="182">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24516,7 +24516,7 @@
         </is>
       </c>
       <c r="AL182" s="3" t="n">
-        <v>45879.64583333334</v>
+        <v>45879.625</v>
       </c>
     </row>
     <row r="183">
@@ -24525,12 +24525,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24648,7 +24648,7 @@
         </is>
       </c>
       <c r="AL183" s="3" t="n">
-        <v>45879.64583333334</v>
+        <v>45879.625</v>
       </c>
     </row>
     <row r="184">
@@ -24657,12 +24657,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24698,13 +24698,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
         </is>
       </c>
       <c r="AL184" s="3" t="n">
-        <v>45879.64583333334</v>
+        <v>45879.63541666666</v>
       </c>
     </row>
     <row r="185">
@@ -24789,12 +24789,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="AL185" s="3" t="n">
-        <v>45879.64583333334</v>
+        <v>45879.63541666666</v>
       </c>
     </row>
     <row r="186">
@@ -24921,27 +24921,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="AL186" s="3" t="n">
-        <v>45879.64583333334</v>
+        <v>45879.63541666666</v>
       </c>
     </row>
     <row r="187">
@@ -25053,27 +25053,27 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25142,10 +25142,10 @@
         <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC187" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD187" t="n">
         <v>0</v>
@@ -25176,7 +25176,7 @@
         </is>
       </c>
       <c r="AL187" s="3" t="n">
-        <v>45879.66666666666</v>
+        <v>45879.64583333334</v>
       </c>
     </row>
     <row r="188">
@@ -25185,12 +25185,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25308,7 +25308,7 @@
         </is>
       </c>
       <c r="AL188" s="3" t="n">
-        <v>45879.66666666666</v>
+        <v>45879.64583333334</v>
       </c>
     </row>
     <row r="189">
@@ -25317,27 +25317,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25358,13 +25358,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -25406,10 +25406,10 @@
         <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD189" t="n">
         <v>0</v>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="AL189" s="3" t="n">
-        <v>45879.66666666666</v>
+        <v>45879.64583333334</v>
       </c>
     </row>
     <row r="190">
@@ -25449,12 +25449,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25490,13 +25490,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -25538,10 +25538,10 @@
         <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC190" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD190" t="n">
         <v>0</v>
@@ -25572,7 +25572,7 @@
         </is>
       </c>
       <c r="AL190" s="3" t="n">
-        <v>45879.66666666666</v>
+        <v>45879.64583333334</v>
       </c>
     </row>
     <row r="191">
@@ -25581,27 +25581,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25622,13 +25622,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25704,7 +25704,7 @@
         </is>
       </c>
       <c r="AL191" s="3" t="n">
-        <v>45879.66666666666</v>
+        <v>45879.64583333334</v>
       </c>
     </row>
     <row r="192">
@@ -25713,12 +25713,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="AL192" s="3" t="n">
-        <v>45879.66666666666</v>
+        <v>45879.64583333334</v>
       </c>
     </row>
     <row r="193">
@@ -25845,27 +25845,27 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25968,7 +25968,7 @@
         </is>
       </c>
       <c r="AL193" s="3" t="n">
-        <v>45879.67708333334</v>
+        <v>45879.64583333334</v>
       </c>
     </row>
     <row r="194">
@@ -25977,12 +25977,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26100,7 +26100,7 @@
         </is>
       </c>
       <c r="AL194" s="3" t="n">
-        <v>45879.67708333334</v>
+        <v>45879.64583333334</v>
       </c>
     </row>
     <row r="195">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26150,13 +26150,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -26192,10 +26192,10 @@
         <v>0</v>
       </c>
       <c r="Z195" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB195" t="n">
         <v>0</v>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="AL195" s="3" t="n">
-        <v>45879.6875</v>
+        <v>45879.64583333334</v>
       </c>
     </row>
     <row r="196">
@@ -26241,27 +26241,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="M196" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N196" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26364,7 +26364,7 @@
         </is>
       </c>
       <c r="AL196" s="3" t="n">
-        <v>45879.6875</v>
+        <v>45879.66666666666</v>
       </c>
     </row>
     <row r="197">
@@ -26373,27 +26373,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="AL197" s="3" t="n">
-        <v>45879.6875</v>
+        <v>45879.66666666666</v>
       </c>
     </row>
     <row r="198">
@@ -26505,12 +26505,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC198" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="AL198" s="3" t="n">
-        <v>45879.70833333334</v>
+        <v>45879.66666666666</v>
       </c>
     </row>
     <row r="199">
@@ -26637,12 +26637,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26726,10 +26726,10 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC199" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
@@ -26760,7 +26760,7 @@
         </is>
       </c>
       <c r="AL199" s="3" t="n">
-        <v>45879.70833333334</v>
+        <v>45879.66666666666</v>
       </c>
     </row>
     <row r="200">
@@ -26769,12 +26769,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26810,13 +26810,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26858,10 +26858,10 @@
         <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC200" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
@@ -26892,7 +26892,7 @@
         </is>
       </c>
       <c r="AL200" s="3" t="n">
-        <v>45879.77083333334</v>
+        <v>45879.66666666666</v>
       </c>
     </row>
     <row r="201">
@@ -26901,27 +26901,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26996,10 +26996,10 @@
         <v>0</v>
       </c>
       <c r="AD201" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE201" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF201" t="n">
         <v>0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="AL201" s="3" t="n">
-        <v>45879.79166666666</v>
+        <v>45879.66666666666</v>
       </c>
     </row>
     <row r="202">
@@ -27033,12 +27033,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27156,7 +27156,7 @@
         </is>
       </c>
       <c r="AL202" s="3" t="n">
-        <v>45879.79166666666</v>
+        <v>45879.67708333334</v>
       </c>
     </row>
     <row r="203">
@@ -27165,12 +27165,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27206,13 +27206,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -27254,10 +27254,10 @@
         <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD203" t="n">
         <v>0</v>
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="AL203" s="3" t="n">
-        <v>45879.79166666666</v>
+        <v>45879.67708333334</v>
       </c>
     </row>
     <row r="204">
@@ -27297,27 +27297,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="M204" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="N204" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC204" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="AL204" s="3" t="n">
-        <v>45879.79166666666</v>
+        <v>45879.6875</v>
       </c>
     </row>
     <row r="205">
@@ -27429,12 +27429,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27512,10 +27512,10 @@
         <v>0</v>
       </c>
       <c r="Z205" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA205" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB205" t="n">
         <v>0</v>
@@ -27552,7 +27552,7 @@
         </is>
       </c>
       <c r="AL205" s="3" t="n">
-        <v>45879.83333333334</v>
+        <v>45879.6875</v>
       </c>
     </row>
     <row r="206">
@@ -27561,27 +27561,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27650,10 +27650,10 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC206" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -27684,7 +27684,7 @@
         </is>
       </c>
       <c r="AL206" s="3" t="n">
-        <v>45879.83333333334</v>
+        <v>45879.6875</v>
       </c>
     </row>
     <row r="207">
@@ -27693,12 +27693,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="M207" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N207" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27776,16 +27776,16 @@
         <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA207" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB207" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC207" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD207" t="n">
         <v>0</v>
@@ -27816,7 +27816,7 @@
         </is>
       </c>
       <c r="AL207" s="3" t="n">
-        <v>45879.85416666666</v>
+        <v>45879.70833333334</v>
       </c>
     </row>
     <row r="208">
@@ -27825,12 +27825,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27840,12 +27840,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27948,7 +27948,7 @@
         </is>
       </c>
       <c r="AL208" s="3" t="n">
-        <v>45879.875</v>
+        <v>45879.70833333334</v>
       </c>
     </row>
     <row r="209">
@@ -27957,12 +27957,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="M209" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N209" t="n">
-        <v>2.15</v>
+        <v>6.6</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28046,16 +28046,16 @@
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC209" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD209" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF209" t="n">
         <v>0</v>
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="AL209" s="3" t="n">
-        <v>45879.875</v>
+        <v>45879.77083333334</v>
       </c>
     </row>
     <row r="210">
@@ -28089,129 +28089,1449 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M210" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N210" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0</v>
+      </c>
+      <c r="V210" t="n">
+        <v>0</v>
+      </c>
+      <c r="W210" t="n">
+        <v>0</v>
+      </c>
+      <c r="X210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL210" s="3" t="n">
+        <v>45879.79166666666</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Pacific FC</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="n">
+        <v>0</v>
+      </c>
+      <c r="V211" t="n">
+        <v>0</v>
+      </c>
+      <c r="W211" t="n">
+        <v>0</v>
+      </c>
+      <c r="X211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL211" s="3" t="n">
+        <v>45879.79166666666</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0</v>
+      </c>
+      <c r="V212" t="n">
+        <v>0</v>
+      </c>
+      <c r="W212" t="n">
+        <v>0</v>
+      </c>
+      <c r="X212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL212" s="3" t="n">
+        <v>45879.79166666666</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M213" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N213" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0</v>
+      </c>
+      <c r="V213" t="n">
+        <v>0</v>
+      </c>
+      <c r="W213" t="n">
+        <v>0</v>
+      </c>
+      <c r="X213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL213" s="3" t="n">
+        <v>45879.79166666666</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M214" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N214" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0</v>
+      </c>
+      <c r="V214" t="n">
+        <v>0</v>
+      </c>
+      <c r="W214" t="n">
+        <v>0</v>
+      </c>
+      <c r="X214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL214" s="3" t="n">
+        <v>45879.79166666666</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>St. Louis City II</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Colorado Rapids II</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0</v>
+      </c>
+      <c r="T215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="n">
+        <v>0</v>
+      </c>
+      <c r="V215" t="n">
+        <v>0</v>
+      </c>
+      <c r="W215" t="n">
+        <v>0</v>
+      </c>
+      <c r="X215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL215" s="3" t="n">
+        <v>45879.83333333334</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Huntsville City</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Carolina Core</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="n">
+        <v>0</v>
+      </c>
+      <c r="V216" t="n">
+        <v>0</v>
+      </c>
+      <c r="W216" t="n">
+        <v>0</v>
+      </c>
+      <c r="X216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL216" s="3" t="n">
+        <v>45879.83333333334</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M217" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N217" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="n">
+        <v>0</v>
+      </c>
+      <c r="T217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="n">
+        <v>0</v>
+      </c>
+      <c r="V217" t="n">
+        <v>0</v>
+      </c>
+      <c r="W217" t="n">
+        <v>0</v>
+      </c>
+      <c r="X217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL217" s="3" t="n">
+        <v>45879.85416666666</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M218" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N218" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>0</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" t="n">
+        <v>0</v>
+      </c>
+      <c r="T218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="n">
+        <v>0</v>
+      </c>
+      <c r="V218" t="n">
+        <v>0</v>
+      </c>
+      <c r="W218" t="n">
+        <v>0</v>
+      </c>
+      <c r="X218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL218" s="3" t="n">
+        <v>45879.875</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>New England II</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Columbus Crew II</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="n">
+        <v>0</v>
+      </c>
+      <c r="T219" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" t="n">
+        <v>0</v>
+      </c>
+      <c r="V219" t="n">
+        <v>0</v>
+      </c>
+      <c r="W219" t="n">
+        <v>0</v>
+      </c>
+      <c r="X219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL219" s="3" t="n">
+        <v>45879.875</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>LA Galaxy</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>Seattle Sounders</t>
         </is>
       </c>
-      <c r="G210" t="n">
-        <v>0</v>
-      </c>
-      <c r="H210" t="n">
-        <v>0</v>
-      </c>
-      <c r="I210" t="n">
-        <v>0</v>
-      </c>
-      <c r="J210" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" t="inlineStr">
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L210" t="n">
+      <c r="L220" t="n">
         <v>2.15</v>
       </c>
-      <c r="M210" t="n">
+      <c r="M220" t="n">
         <v>3.25</v>
       </c>
-      <c r="N210" t="n">
+      <c r="N220" t="n">
         <v>3.25</v>
       </c>
-      <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="P210" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="n">
-        <v>0</v>
-      </c>
-      <c r="T210" t="n">
-        <v>0</v>
-      </c>
-      <c r="U210" t="n">
-        <v>0</v>
-      </c>
-      <c r="V210" t="n">
-        <v>0</v>
-      </c>
-      <c r="W210" t="n">
-        <v>0</v>
-      </c>
-      <c r="X210" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y210" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB210" t="n">
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="n">
+        <v>0</v>
+      </c>
+      <c r="V220" t="n">
+        <v>0</v>
+      </c>
+      <c r="W220" t="n">
+        <v>0</v>
+      </c>
+      <c r="X220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB220" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC210" t="n">
+      <c r="AC220" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD210" t="n">
+      <c r="AD220" t="n">
         <v>2.47</v>
       </c>
-      <c r="AE210" t="n">
+      <c r="AE220" t="n">
         <v>1.54</v>
       </c>
-      <c r="AF210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL210" s="3" t="n">
+      <c r="AF220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL220" s="3" t="n">
         <v>45879.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-10.xlsx
+++ b/jogos_2025-08-10.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2432,16 +2432,16 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,10 +2696,10 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.69</v>
+        <v>5.3</v>
       </c>
       <c r="M52" t="n">
-        <v>3.75</v>
+        <v>4.02</v>
       </c>
       <c r="N52" t="n">
-        <v>4.5</v>
+        <v>1.63</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,7 +7322,7 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC52" t="n">
         <v>2.05</v>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8294,22 +8294,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,22 +14234,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.64</v>
+        <v>3.94</v>
       </c>
       <c r="M105" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="N105" t="n">
-        <v>2.64</v>
+        <v>1.88</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14318,10 +14318,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16478,22 +16478,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16874,22 +16874,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17534,22 +17534,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20342,13 +20342,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -20384,16 +20384,16 @@
         <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC151" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD151" t="n">
         <v>0</v>
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20834,22 +20834,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21230,22 +21230,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21440,16 +21440,16 @@
         <v>0</v>
       </c>
       <c r="Z159" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23474,22 +23474,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23510,13 +23510,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23558,10 +23558,10 @@
         <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC175" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD175" t="n">
         <v>0</v>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23738,22 +23738,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23870,7 +23870,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23906,13 +23906,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23954,10 +23954,10 @@
         <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD178" t="n">
         <v>0</v>
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24134,22 +24134,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -25058,22 +25058,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25190,22 +25190,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25322,7 +25322,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -25332,12 +25332,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25358,13 +25358,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -25454,22 +25454,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25586,22 +25586,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25622,13 +25622,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25982,22 +25982,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26114,22 +26114,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC197" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.27</v>
+        <v>1.41</v>
       </c>
       <c r="M198" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="N198" t="n">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26642,7 +26642,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="M199" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N199" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26726,10 +26726,10 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AC199" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
@@ -26774,22 +26774,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26906,22 +26906,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28184,10 +28184,10 @@
         <v>0</v>
       </c>
       <c r="AD210" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE210" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF210" t="n">
         <v>0</v>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC211" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28448,10 +28448,10 @@
         <v>0</v>
       </c>
       <c r="AD212" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF212" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28658,13 +28658,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28706,10 +28706,10 @@
         <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC214" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD214" t="n">
         <v>0</v>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29186,13 +29186,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -29240,10 +29240,10 @@
         <v>0</v>
       </c>
       <c r="AD218" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF218" t="n">
         <v>0</v>
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29318,13 +29318,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -29372,10 +29372,10 @@
         <v>0</v>
       </c>
       <c r="AD219" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE219" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF219" t="n">
         <v>0</v>

--- a/jogos_2025-08-10.xlsx
+++ b/jogos_2025-08-10.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,10 +3488,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,16 +6926,16 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>5.3</v>
+        <v>1.15</v>
       </c>
       <c r="M52" t="n">
-        <v>4.02</v>
+        <v>7</v>
       </c>
       <c r="N52" t="n">
-        <v>1.63</v>
+        <v>15</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,16 +7322,16 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N71" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="M88" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N88" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13706,22 +13706,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18272,16 +18272,16 @@
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20342,13 +20342,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -20384,16 +20384,16 @@
         <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD151" t="n">
         <v>0</v>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22154,22 +22154,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22418,22 +22418,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23510,13 +23510,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23558,10 +23558,10 @@
         <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD175" t="n">
         <v>0</v>
@@ -23606,22 +23606,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23738,22 +23738,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23774,13 +23774,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23822,10 +23822,10 @@
         <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC177" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD177" t="n">
         <v>0</v>
@@ -23870,7 +23870,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,22 +24002,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24134,22 +24134,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24266,22 +24266,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25190,22 +25190,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25358,13 +25358,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -25454,7 +25454,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25850,22 +25850,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26150,13 +26150,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC196" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26642,22 +26642,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26726,10 +26726,10 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
@@ -26774,22 +26774,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC201" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.32</v>
+        <v>2.05</v>
       </c>
       <c r="M204" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="N204" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC204" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC204" t="n">
-        <v>2.05</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27434,22 +27434,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="M205" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="N205" t="n">
-        <v>2.85</v>
+        <v>8.4</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27512,16 +27512,16 @@
         <v>0</v>
       </c>
       <c r="Z205" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC205" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27566,22 +27566,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M206" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N206" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27644,16 +27644,16 @@
         <v>0</v>
       </c>
       <c r="Z206" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA206" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB206" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC210" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC213" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28658,13 +28658,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28706,10 +28706,10 @@
         <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC214" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD214" t="n">
         <v>0</v>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29186,13 +29186,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -29240,10 +29240,10 @@
         <v>0</v>
       </c>
       <c r="AD218" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE218" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF218" t="n">
         <v>0</v>
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29318,13 +29318,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -29372,10 +29372,10 @@
         <v>0</v>
       </c>
       <c r="AD219" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE219" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF219" t="n">
         <v>0</v>

--- a/jogos_2025-08-10.xlsx
+++ b/jogos_2025-08-10.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.43</v>
+        <v>1.94</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>5.3</v>
+        <v>1.15</v>
       </c>
       <c r="M48" t="n">
-        <v>4.02</v>
+        <v>7</v>
       </c>
       <c r="N48" t="n">
-        <v>1.63</v>
+        <v>15</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,16 +6794,16 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.15</v>
+        <v>5.3</v>
       </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>4.02</v>
       </c>
       <c r="N52" t="n">
-        <v>15</v>
+        <v>1.63</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,16 +7322,16 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AC52" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,22 +8030,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="M89" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N89" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14318,10 +14318,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,22 +15818,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16478,22 +16478,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17270,22 +17270,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17534,22 +17534,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18272,16 +18272,16 @@
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20342,13 +20342,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -20384,16 +20384,16 @@
         <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC151" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD151" t="n">
         <v>0</v>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23210,22 +23210,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23342,22 +23342,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23774,13 +23774,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23822,10 +23822,10 @@
         <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD177" t="n">
         <v>0</v>
@@ -23870,7 +23870,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23906,13 +23906,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23954,10 +23954,10 @@
         <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC178" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD178" t="n">
         <v>0</v>
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25190,22 +25190,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25454,22 +25454,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25586,22 +25586,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25622,13 +25622,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25850,22 +25850,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26150,13 +26150,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC197" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="M198" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N198" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26810,13 +26810,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26858,10 +26858,10 @@
         <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC200" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC201" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,58 +27338,58 @@
         </is>
       </c>
       <c r="L204" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M204" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N204" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="n">
+        <v>0</v>
+      </c>
+      <c r="T204" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" t="n">
+        <v>0</v>
+      </c>
+      <c r="V204" t="n">
+        <v>0</v>
+      </c>
+      <c r="W204" t="n">
+        <v>0</v>
+      </c>
+      <c r="X204" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC204" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M204" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N204" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O204" t="n">
-        <v>0</v>
-      </c>
-      <c r="P204" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0</v>
-      </c>
-      <c r="S204" t="n">
-        <v>0</v>
-      </c>
-      <c r="T204" t="n">
-        <v>0</v>
-      </c>
-      <c r="U204" t="n">
-        <v>0</v>
-      </c>
-      <c r="V204" t="n">
-        <v>0</v>
-      </c>
-      <c r="W204" t="n">
-        <v>0</v>
-      </c>
-      <c r="X204" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y204" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z204" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA204" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB204" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC204" t="n">
-        <v>1.7</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27434,22 +27434,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="M205" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="N205" t="n">
-        <v>8.4</v>
+        <v>2.85</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27512,16 +27512,16 @@
         <v>0</v>
       </c>
       <c r="Z205" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA205" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB205" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC205" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27566,22 +27566,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="M206" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N206" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27644,16 +27644,16 @@
         <v>0</v>
       </c>
       <c r="Z206" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC206" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC210" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC211" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC213" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28658,13 +28658,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28706,10 +28706,10 @@
         <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC214" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD214" t="n">
         <v>0</v>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29186,13 +29186,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -29240,10 +29240,10 @@
         <v>0</v>
       </c>
       <c r="AD218" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF218" t="n">
         <v>0</v>
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29318,13 +29318,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -29372,10 +29372,10 @@
         <v>0</v>
       </c>
       <c r="AD219" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE219" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF219" t="n">
         <v>0</v>

--- a/jogos_2025-08-10.xlsx
+++ b/jogos_2025-08-10.xlsx
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.85</v>
+        <v>1.69</v>
       </c>
       <c r="M58" t="n">
-        <v>3.21</v>
+        <v>3.83</v>
       </c>
       <c r="N58" t="n">
-        <v>2.49</v>
+        <v>4.38</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15818,22 +15818,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.77</v>
+        <v>3.55</v>
       </c>
       <c r="M117" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="N117" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AC117" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.55</v>
+        <v>2.17</v>
       </c>
       <c r="M118" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N118" t="n">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,22 +16082,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.17</v>
+        <v>3.77</v>
       </c>
       <c r="M119" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="N119" t="n">
-        <v>3.2</v>
+        <v>2.04</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.74</v>
+        <v>2.19</v>
       </c>
       <c r="AC119" t="n">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17270,22 +17270,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2025-08-10.xlsx
+++ b/jogos_2025-08-10.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.72</v>
+        <v>2.46</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.21</v>
+        <v>3.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>1.83</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.43</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M20" t="n">
         <v>3.6</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N20" t="n">
-        <v>1.83</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,16 +6794,16 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.69</v>
+        <v>1.15</v>
       </c>
       <c r="M50" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="N50" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,16 +7058,16 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15026,22 +15026,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15422,22 +15422,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.08</v>
+        <v>3.77</v>
       </c>
       <c r="M114" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="N114" t="n">
-        <v>3.45</v>
+        <v>2.04</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,22 +16082,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.77</v>
+        <v>2.08</v>
       </c>
       <c r="M119" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="N119" t="n">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.69</v>
+        <v>6.35</v>
       </c>
       <c r="M126" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N126" t="n">
-        <v>4.8</v>
+        <v>1.48</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17534,22 +17534,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18536,16 +18536,16 @@
         <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20342,13 +20342,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -20384,16 +20384,16 @@
         <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD151" t="n">
         <v>0</v>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21098,22 +21098,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21230,22 +21230,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -22154,22 +22154,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22418,22 +22418,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -23162,10 +23162,10 @@
         <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC172" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD172" t="n">
         <v>0</v>
@@ -23474,7 +23474,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23774,13 +23774,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23822,10 +23822,10 @@
         <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC177" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD177" t="n">
         <v>0</v>
@@ -23870,7 +23870,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23906,13 +23906,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23954,10 +23954,10 @@
         <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD178" t="n">
         <v>0</v>
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24662,7 +24662,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24698,13 +24698,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="M184" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="N184" t="n">
-        <v>5.2</v>
+        <v>7.9</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24830,13 +24830,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24884,10 +24884,10 @@
         <v>0</v>
       </c>
       <c r="AD185" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE185" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF185" t="n">
         <v>0</v>
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24962,13 +24962,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -25058,22 +25058,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25190,22 +25190,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25586,22 +25586,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25622,13 +25622,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25850,22 +25850,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26150,13 +26150,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC196" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="M198" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N198" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26810,13 +26810,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26858,10 +26858,10 @@
         <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC200" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC201" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.32</v>
+        <v>2.05</v>
       </c>
       <c r="M204" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="N204" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC204" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC204" t="n">
-        <v>2.05</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27434,22 +27434,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="M205" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="N205" t="n">
-        <v>2.85</v>
+        <v>8.4</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27512,16 +27512,16 @@
         <v>0</v>
       </c>
       <c r="Z205" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC205" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27566,22 +27566,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M206" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N206" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27644,16 +27644,16 @@
         <v>0</v>
       </c>
       <c r="Z206" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA206" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB206" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC210" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="M211" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N211" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,16 +28310,16 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD211" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF211" t="n">
         <v>0</v>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28448,10 +28448,10 @@
         <v>0</v>
       </c>
       <c r="AD212" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
         <v>0</v>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC213" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28658,13 +28658,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28706,10 +28706,10 @@
         <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC214" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD214" t="n">
         <v>0</v>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29186,13 +29186,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -29240,10 +29240,10 @@
         <v>0</v>
       </c>
       <c r="AD218" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE218" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF218" t="n">
         <v>0</v>
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29318,13 +29318,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -29372,10 +29372,10 @@
         <v>0</v>
       </c>
       <c r="AD219" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE219" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF219" t="n">
         <v>0</v>

--- a/jogos_2025-08-10.xlsx
+++ b/jogos_2025-08-10.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.43</v>
+        <v>1.94</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.6</v>
+        <v>2.21</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.83</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,55 +3182,55 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.81</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
         <v>1.95</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,10 +3488,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="M38" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="M39" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5612,10 +5612,10 @@
         <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6008,10 +6008,10 @@
         <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.29</v>
+        <v>1.56</v>
       </c>
       <c r="M44" t="n">
-        <v>3.32</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.17</v>
+        <v>4.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,16 +7058,16 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.69</v>
+        <v>5.3</v>
       </c>
       <c r="M51" t="n">
-        <v>3.75</v>
+        <v>4.02</v>
       </c>
       <c r="N51" t="n">
-        <v>4.5</v>
+        <v>1.63</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
         <v>2.05</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,16 +7322,16 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>4.6</v>
+        <v>1.39</v>
       </c>
       <c r="M78" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N78" t="n">
-        <v>1.62</v>
+        <v>7.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AC78" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13706,22 +13706,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.17</v>
+        <v>3.94</v>
       </c>
       <c r="M104" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="N104" t="n">
-        <v>3.2</v>
+        <v>1.88</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC104" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="M106" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="N106" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC106" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14762,22 +14762,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15026,22 +15026,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15422,22 +15422,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.64</v>
+        <v>3.12</v>
       </c>
       <c r="M115" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N115" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,22 +15686,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15770,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD116" t="n">
         <v>0</v>
@@ -15818,22 +15818,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.69</v>
+        <v>6.35</v>
       </c>
       <c r="M123" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N123" t="n">
-        <v>4.8</v>
+        <v>1.48</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>6.35</v>
+        <v>2.18</v>
       </c>
       <c r="M126" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N126" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -22454,13 +22454,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -22502,10 +22502,10 @@
         <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC167" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD167" t="n">
         <v>0</v>
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD174" t="n">
         <v>0</v>
@@ -23510,13 +23510,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -24086,10 +24086,10 @@
         <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC179" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD179" t="n">
         <v>0</v>
@@ -24170,13 +24170,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -24434,13 +24434,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -24476,10 +24476,10 @@
         <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA182" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB182" t="n">
         <v>0</v>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24614,10 +24614,10 @@
         <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC183" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD183" t="n">
         <v>0</v>
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25928,10 +25928,10 @@
         <v>0</v>
       </c>
       <c r="Z193" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA193" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB193" t="n">
         <v>0</v>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28316,10 +28316,10 @@
         <v>0</v>
       </c>
       <c r="AD211" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
         <v>0</v>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC213" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28658,13 +28658,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="M214" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N214" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28706,16 +28706,16 @@
         <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC214" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD214" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE214" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF214" t="n">
         <v>0</v>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29186,13 +29186,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -29240,10 +29240,10 @@
         <v>0</v>
       </c>
       <c r="AD218" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF218" t="n">
         <v>0</v>
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29318,13 +29318,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -29372,10 +29372,10 @@
         <v>0</v>
       </c>
       <c r="AD219" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE219" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF219" t="n">
         <v>0</v>

--- a/jogos_2025-08-10.xlsx
+++ b/jogos_2025-08-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL220"/>
+  <dimension ref="A1:AL221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.43</v>
+        <v>1.83</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>2.43</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>1.94</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.6</v>
+        <v>2.46</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.21</v>
+        <v>3.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>1.94</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>2.85</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.34</v>
+        <v>1.79</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>2.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.4</v>
+        <v>2.21</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6008,10 +6008,10 @@
         <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6272,10 +6272,10 @@
         <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.69</v>
+        <v>1.15</v>
       </c>
       <c r="M48" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="N48" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,16 +6794,16 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,16 +7322,16 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,22 +8030,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.39</v>
+        <v>4.6</v>
       </c>
       <c r="M78" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N78" t="n">
-        <v>7.2</v>
+        <v>1.62</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,22 +13046,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="M96" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N96" t="n">
-        <v>3.95</v>
+        <v>2.19</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,22 +14234,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14324,10 +14324,10 @@
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF105" t="n">
         <v>0</v>
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="M106" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N106" t="n">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15158,22 +15158,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>3.12</v>
+        <v>2.08</v>
       </c>
       <c r="M115" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N115" t="n">
-        <v>2.32</v>
+        <v>3.45</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15770,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
         <v>0</v>
@@ -15818,22 +15818,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16610,22 +16610,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.69</v>
+        <v>2.18</v>
       </c>
       <c r="M124" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N124" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC124" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.18</v>
+        <v>6.35</v>
       </c>
       <c r="M126" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N126" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18536,16 +18536,16 @@
         <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19592,16 +19592,16 @@
         <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC145" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD145" t="n">
         <v>0</v>
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.79</v>
+        <v>4.5</v>
       </c>
       <c r="M153" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N153" t="n">
-        <v>4.3</v>
+        <v>1.65</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21098,22 +21098,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22017,12 +22017,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22140,7 +22140,7 @@
         </is>
       </c>
       <c r="AL164" s="3" t="n">
-        <v>45879.55208333334</v>
+        <v>45879.54166666666</v>
       </c>
     </row>
     <row r="165">
@@ -22149,12 +22149,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -22164,12 +22164,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="AL165" s="3" t="n">
-        <v>45879.5625</v>
+        <v>45879.55208333334</v>
       </c>
     </row>
     <row r="166">
@@ -22545,27 +22545,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="AL168" s="3" t="n">
-        <v>45879.57291666666</v>
+        <v>45879.5625</v>
       </c>
     </row>
     <row r="169">
@@ -22677,12 +22677,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22800,7 +22800,7 @@
         </is>
       </c>
       <c r="AL169" s="3" t="n">
-        <v>45879.58333333334</v>
+        <v>45879.57291666666</v>
       </c>
     </row>
     <row r="170">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22850,13 +22850,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22898,10 +22898,10 @@
         <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC170" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD170" t="n">
         <v>0</v>
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -23162,10 +23162,10 @@
         <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD172" t="n">
         <v>0</v>
@@ -23205,27 +23205,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AL173" s="3" t="n">
-        <v>45879.59375</v>
+        <v>45879.58333333334</v>
       </c>
     </row>
     <row r="174">
@@ -23342,22 +23342,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2.04</v>
+        <v>2.85</v>
       </c>
       <c r="M174" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N174" t="n">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -23426,16 +23426,16 @@
         <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD174" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE174" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF174" t="n">
         <v>0</v>
@@ -23469,12 +23469,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23510,13 +23510,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="M175" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N175" t="n">
-        <v>2.09</v>
+        <v>3.4</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23558,10 +23558,10 @@
         <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD175" t="n">
         <v>0</v>
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="AL175" s="3" t="n">
-        <v>45879.60416666666</v>
+        <v>45879.59375</v>
       </c>
     </row>
     <row r="176">
@@ -23606,22 +23606,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23642,13 +23642,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23690,10 +23690,10 @@
         <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC176" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD176" t="n">
         <v>0</v>
@@ -23738,22 +23738,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23774,13 +23774,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23822,10 +23822,10 @@
         <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD177" t="n">
         <v>0</v>
@@ -23997,27 +23997,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="M179" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N179" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -24086,10 +24086,10 @@
         <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD179" t="n">
         <v>0</v>
@@ -24120,7 +24120,7 @@
         </is>
       </c>
       <c r="AL179" s="3" t="n">
-        <v>45879.625</v>
+        <v>45879.60416666666</v>
       </c>
     </row>
     <row r="180">
@@ -24134,22 +24134,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24170,13 +24170,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="M180" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N180" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -24218,10 +24218,10 @@
         <v>0</v>
       </c>
       <c r="AB180" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC180" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD180" t="n">
         <v>0</v>
@@ -24266,7 +24266,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24302,13 +24302,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24434,13 +24434,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="M182" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N182" t="n">
-        <v>2.63</v>
+        <v>3.95</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -24476,16 +24476,16 @@
         <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC182" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD182" t="n">
         <v>0</v>
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="M183" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N183" t="n">
-        <v>3.95</v>
+        <v>2.63</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24608,16 +24608,16 @@
         <v>0</v>
       </c>
       <c r="Z183" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB183" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD183" t="n">
         <v>0</v>
@@ -24657,12 +24657,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24698,13 +24698,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
         </is>
       </c>
       <c r="AL184" s="3" t="n">
-        <v>45879.63541666666</v>
+        <v>45879.625</v>
       </c>
     </row>
     <row r="185">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24830,13 +24830,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>1.51</v>
+        <v>4.61</v>
       </c>
       <c r="M185" t="n">
         <v>4</v>
       </c>
       <c r="N185" t="n">
-        <v>5.2</v>
+        <v>1.72</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24884,10 +24884,10 @@
         <v>0</v>
       </c>
       <c r="AD185" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF185" t="n">
         <v>0</v>
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24962,13 +24962,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>4.61</v>
+        <v>1.37</v>
       </c>
       <c r="M186" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="N186" t="n">
-        <v>1.72</v>
+        <v>7.9</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25148,10 +25148,10 @@
         <v>0</v>
       </c>
       <c r="AD187" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE187" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF187" t="n">
         <v>0</v>
@@ -25176,7 +25176,7 @@
         </is>
       </c>
       <c r="AL187" s="3" t="n">
-        <v>45879.64583333334</v>
+        <v>45879.63541666666</v>
       </c>
     </row>
     <row r="188">
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25454,22 +25454,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25754,13 +25754,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25796,10 +25796,10 @@
         <v>0</v>
       </c>
       <c r="Z192" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA192" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB192" t="n">
         <v>0</v>
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25928,10 +25928,10 @@
         <v>0</v>
       </c>
       <c r="Z193" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA193" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB193" t="n">
         <v>0</v>
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26241,12 +26241,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26364,7 +26364,7 @@
         </is>
       </c>
       <c r="AL196" s="3" t="n">
-        <v>45879.66666666666</v>
+        <v>45879.64583333334</v>
       </c>
     </row>
     <row r="197">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="M198" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N198" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26642,22 +26642,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26726,10 +26726,10 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC199" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26810,13 +26810,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26858,10 +26858,10 @@
         <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC200" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
@@ -26906,22 +26906,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC201" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27033,12 +27033,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27156,7 +27156,7 @@
         </is>
       </c>
       <c r="AL202" s="3" t="n">
-        <v>45879.67708333334</v>
+        <v>45879.66666666666</v>
       </c>
     </row>
     <row r="203">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27297,27 +27297,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="AL204" s="3" t="n">
-        <v>45879.6875</v>
+        <v>45879.67708333334</v>
       </c>
     </row>
     <row r="205">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.32</v>
+        <v>2.05</v>
       </c>
       <c r="M205" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="N205" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC205" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC205" t="n">
-        <v>2.05</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27566,22 +27566,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="M206" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="N206" t="n">
-        <v>2.85</v>
+        <v>8.4</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27644,16 +27644,16 @@
         <v>0</v>
       </c>
       <c r="Z206" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC206" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -27693,7 +27693,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="M207" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N207" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27776,10 +27776,10 @@
         <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA207" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AB207" t="n">
         <v>0</v>
@@ -27816,7 +27816,7 @@
         </is>
       </c>
       <c r="AL207" s="3" t="n">
-        <v>45879.70833333334</v>
+        <v>45879.6875</v>
       </c>
     </row>
     <row r="208">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27840,12 +27840,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27866,13 +27866,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27908,10 +27908,10 @@
         <v>0</v>
       </c>
       <c r="Z208" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA208" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB208" t="n">
         <v>0</v>
@@ -27957,12 +27957,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28046,10 +28046,10 @@
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC209" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD209" t="n">
         <v>0</v>
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="AL209" s="3" t="n">
-        <v>45879.77083333334</v>
+        <v>45879.70833333334</v>
       </c>
     </row>
     <row r="210">
@@ -28089,12 +28089,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="M210" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N210" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC210" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="AL210" s="3" t="n">
-        <v>45879.79166666666</v>
+        <v>45879.77083333334</v>
       </c>
     </row>
     <row r="211">
@@ -28358,7 +28358,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28448,10 +28448,10 @@
         <v>0</v>
       </c>
       <c r="AD212" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF212" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28658,13 +28658,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28712,10 +28712,10 @@
         <v>0</v>
       </c>
       <c r="AD214" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE214" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF214" t="n">
         <v>0</v>
@@ -28749,12 +28749,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28764,12 +28764,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28790,13 +28790,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28838,10 +28838,10 @@
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC215" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD215" t="n">
         <v>0</v>
@@ -28872,7 +28872,7 @@
         </is>
       </c>
       <c r="AL215" s="3" t="n">
-        <v>45879.83333333334</v>
+        <v>45879.79166666666</v>
       </c>
     </row>
     <row r="216">
@@ -29013,12 +29013,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29102,10 +29102,10 @@
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD217" t="n">
         <v>0</v>
@@ -29136,7 +29136,7 @@
         </is>
       </c>
       <c r="AL217" s="3" t="n">
-        <v>45879.85416666666</v>
+        <v>45879.83333333334</v>
       </c>
     </row>
     <row r="218">
@@ -29145,12 +29145,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29186,13 +29186,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -29234,10 +29234,10 @@
         <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC218" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD218" t="n">
         <v>0</v>
@@ -29268,7 +29268,7 @@
         </is>
       </c>
       <c r="AL218" s="3" t="n">
-        <v>45879.875</v>
+        <v>45879.85416666666</v>
       </c>
     </row>
     <row r="219">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29318,13 +29318,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -29372,10 +29372,10 @@
         <v>0</v>
       </c>
       <c r="AD219" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE219" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF219" t="n">
         <v>0</v>
@@ -29409,7 +29409,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29450,88 +29450,220 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="M220" t="n">
         <v>3.25</v>
       </c>
       <c r="N220" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="n">
+        <v>0</v>
+      </c>
+      <c r="V220" t="n">
+        <v>0</v>
+      </c>
+      <c r="W220" t="n">
+        <v>0</v>
+      </c>
+      <c r="X220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL220" s="3" t="n">
+        <v>45879.875</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M221" t="n">
         <v>3.25</v>
       </c>
-      <c r="O220" t="n">
-        <v>0</v>
-      </c>
-      <c r="P220" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
-      <c r="R220" t="n">
-        <v>0</v>
-      </c>
-      <c r="S220" t="n">
-        <v>0</v>
-      </c>
-      <c r="T220" t="n">
-        <v>0</v>
-      </c>
-      <c r="U220" t="n">
-        <v>0</v>
-      </c>
-      <c r="V220" t="n">
-        <v>0</v>
-      </c>
-      <c r="W220" t="n">
-        <v>0</v>
-      </c>
-      <c r="X220" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y220" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z220" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA220" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB220" t="n">
+      <c r="N221" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>0</v>
+      </c>
+      <c r="V221" t="n">
+        <v>0</v>
+      </c>
+      <c r="W221" t="n">
+        <v>0</v>
+      </c>
+      <c r="X221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB221" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC220" t="n">
+      <c r="AC221" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD220" t="n">
+      <c r="AD221" t="n">
         <v>2.47</v>
       </c>
-      <c r="AE220" t="n">
+      <c r="AE221" t="n">
         <v>1.54</v>
       </c>
-      <c r="AF220" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG220" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH220" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI220" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL220" s="3" t="n">
+      <c r="AF221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL221" s="3" t="n">
         <v>45879.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-10.xlsx
+++ b/jogos_2025-08-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL221"/>
+  <dimension ref="A1:AL223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.43</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.46</v>
+        <v>1.81</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.81</v>
+        <v>2.46</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.4</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>3.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>8.5</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
         <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,22 +8030,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="M86" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N86" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="M94" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N94" t="n">
-        <v>1.64</v>
+        <v>2.19</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC94" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="M96" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N96" t="n">
-        <v>2.19</v>
+        <v>1.64</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13706,22 +13706,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,22 +14234,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14324,10 +14324,10 @@
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
         <v>0</v>
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.12</v>
+        <v>1.73</v>
       </c>
       <c r="M107" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N107" t="n">
-        <v>2.32</v>
+        <v>3.95</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14846,10 +14846,10 @@
         <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD109" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15158,22 +15158,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,22 +15422,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3.94</v>
+        <v>2.64</v>
       </c>
       <c r="M114" t="n">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="N114" t="n">
-        <v>1.88</v>
+        <v>2.64</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC114" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="M115" t="n">
         <v>3.25</v>
       </c>
       <c r="N115" t="n">
-        <v>3.45</v>
+        <v>2.22</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15776,10 +15776,10 @@
         <v>0</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF116" t="n">
         <v>0</v>
@@ -15818,22 +15818,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.55</v>
+        <v>2.08</v>
       </c>
       <c r="M121" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N121" t="n">
-        <v>1.98</v>
+        <v>3.45</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16610,22 +16610,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,22 +19250,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19592,16 +19592,16 @@
         <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD145" t="n">
         <v>0</v>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20474,13 +20474,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="M153" t="n">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="N153" t="n">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20648,16 +20648,16 @@
         <v>0</v>
       </c>
       <c r="Z153" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC153" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD153" t="n">
         <v>0</v>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22022,22 +22022,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22418,22 +22418,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22454,13 +22454,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -22502,10 +22502,10 @@
         <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD167" t="n">
         <v>0</v>
@@ -22550,22 +22550,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22634,10 +22634,10 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD168" t="n">
         <v>0</v>
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22850,13 +22850,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22898,10 +22898,10 @@
         <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC170" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD170" t="n">
         <v>0</v>
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -23162,10 +23162,10 @@
         <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC172" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD172" t="n">
         <v>0</v>
@@ -23342,22 +23342,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2.85</v>
+        <v>2.04</v>
       </c>
       <c r="M174" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N174" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -23426,16 +23426,16 @@
         <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD174" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF174" t="n">
         <v>0</v>
@@ -23474,22 +23474,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23510,13 +23510,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>2.04</v>
+        <v>2.85</v>
       </c>
       <c r="M175" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N175" t="n">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23558,16 +23558,16 @@
         <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD175" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE175" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF175" t="n">
         <v>0</v>
@@ -23606,22 +23606,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23642,13 +23642,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23690,10 +23690,10 @@
         <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC176" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD176" t="n">
         <v>0</v>
@@ -23738,22 +23738,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23774,13 +23774,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23870,7 +23870,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23906,13 +23906,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23954,10 +23954,10 @@
         <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC178" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD178" t="n">
         <v>0</v>
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24830,13 +24830,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>4.61</v>
+        <v>1.37</v>
       </c>
       <c r="M185" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="N185" t="n">
-        <v>1.72</v>
+        <v>7.9</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24962,13 +24962,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>1.37</v>
+        <v>4.61</v>
       </c>
       <c r="M186" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="N186" t="n">
-        <v>7.9</v>
+        <v>1.72</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -25190,22 +25190,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25454,22 +25454,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25490,13 +25490,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -25532,10 +25532,10 @@
         <v>0</v>
       </c>
       <c r="Z190" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA190" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB190" t="n">
         <v>0</v>
@@ -25586,22 +25586,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25754,13 +25754,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25796,10 +25796,10 @@
         <v>0</v>
       </c>
       <c r="Z192" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB192" t="n">
         <v>0</v>
@@ -25850,22 +25850,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26018,13 +26018,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26150,13 +26150,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -26246,22 +26246,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="M198" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N198" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26642,7 +26642,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26726,10 +26726,10 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
@@ -26774,22 +26774,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26810,13 +26810,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26858,10 +26858,10 @@
         <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC200" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
@@ -26906,22 +26906,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC201" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC202" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27165,12 +27165,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27206,13 +27206,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -27254,10 +27254,10 @@
         <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC203" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD203" t="n">
         <v>0</v>
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="AL203" s="3" t="n">
-        <v>45879.67708333334</v>
+        <v>45879.66666666666</v>
       </c>
     </row>
     <row r="204">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27429,27 +27429,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC205" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27552,7 +27552,7 @@
         </is>
       </c>
       <c r="AL205" s="3" t="n">
-        <v>45879.6875</v>
+        <v>45879.67708333334</v>
       </c>
     </row>
     <row r="206">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.32</v>
+        <v>2.05</v>
       </c>
       <c r="M206" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="N206" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27650,10 +27650,10 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC206" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC206" t="n">
-        <v>2.05</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -27698,22 +27698,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="M207" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="N207" t="n">
-        <v>2.85</v>
+        <v>8.4</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27776,16 +27776,16 @@
         <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC207" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD207" t="n">
         <v>0</v>
@@ -27825,7 +27825,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -27840,12 +27840,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27866,13 +27866,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="M208" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N208" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27908,10 +27908,10 @@
         <v>0</v>
       </c>
       <c r="Z208" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA208" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AB208" t="n">
         <v>0</v>
@@ -27948,7 +27948,7 @@
         </is>
       </c>
       <c r="AL208" s="3" t="n">
-        <v>45879.70833333334</v>
+        <v>45879.6875</v>
       </c>
     </row>
     <row r="209">
@@ -28089,12 +28089,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="M210" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N210" t="n">
-        <v>6.6</v>
+        <v>3.05</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28172,16 +28172,16 @@
         <v>0</v>
       </c>
       <c r="Z210" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA210" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB210" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC210" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="AL210" s="3" t="n">
-        <v>45879.77083333334</v>
+        <v>45879.70833333334</v>
       </c>
     </row>
     <row r="211">
@@ -28221,12 +28221,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC211" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28344,7 +28344,7 @@
         </is>
       </c>
       <c r="AL211" s="3" t="n">
-        <v>45879.79166666666</v>
+        <v>45879.77083333334</v>
       </c>
     </row>
     <row r="212">
@@ -28353,12 +28353,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="M212" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="N212" t="n">
-        <v>4.8</v>
+        <v>4.17</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28448,10 +28448,10 @@
         <v>0</v>
       </c>
       <c r="AD212" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
         <v>0</v>
@@ -28476,7 +28476,7 @@
         </is>
       </c>
       <c r="AL212" s="3" t="n">
-        <v>45879.79166666666</v>
+        <v>45879.77083333334</v>
       </c>
     </row>
     <row r="213">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="M213" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N213" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,16 +28574,16 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC213" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD213" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE213" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF213" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28658,13 +28658,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28706,10 +28706,10 @@
         <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC214" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD214" t="n">
         <v>0</v>
@@ -28754,7 +28754,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28764,12 +28764,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28790,13 +28790,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28838,10 +28838,10 @@
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC215" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD215" t="n">
         <v>0</v>
@@ -28881,12 +28881,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28922,13 +28922,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28970,10 +28970,10 @@
         <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC216" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD216" t="n">
         <v>0</v>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="AL216" s="3" t="n">
-        <v>45879.83333333334</v>
+        <v>45879.79166666666</v>
       </c>
     </row>
     <row r="217">
@@ -29013,12 +29013,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29136,7 +29136,7 @@
         </is>
       </c>
       <c r="AL217" s="3" t="n">
-        <v>45879.83333333334</v>
+        <v>45879.79166666666</v>
       </c>
     </row>
     <row r="218">
@@ -29145,12 +29145,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29186,13 +29186,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -29234,10 +29234,10 @@
         <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC218" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD218" t="n">
         <v>0</v>
@@ -29268,7 +29268,7 @@
         </is>
       </c>
       <c r="AL218" s="3" t="n">
-        <v>45879.85416666666</v>
+        <v>45879.83333333334</v>
       </c>
     </row>
     <row r="219">
@@ -29277,7 +29277,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="AL219" s="3" t="n">
-        <v>45879.875</v>
+        <v>45879.83333333334</v>
       </c>
     </row>
     <row r="220">
@@ -29409,12 +29409,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29450,13 +29450,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="M220" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N220" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -29498,16 +29498,16 @@
         <v>0</v>
       </c>
       <c r="AB220" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC220" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD220" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF220" t="n">
         <v>0</v>
@@ -29532,7 +29532,7 @@
         </is>
       </c>
       <c r="AL220" s="3" t="n">
-        <v>45879.875</v>
+        <v>45879.85416666666</v>
       </c>
     </row>
     <row r="221">
@@ -29541,7 +29541,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -29556,12 +29556,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29582,88 +29582,352 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="M221" t="n">
         <v>3.25</v>
       </c>
       <c r="N221" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>0</v>
+      </c>
+      <c r="V221" t="n">
+        <v>0</v>
+      </c>
+      <c r="W221" t="n">
+        <v>0</v>
+      </c>
+      <c r="X221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL221" s="3" t="n">
+        <v>45879.875</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>New England II</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Columbus Crew II</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>0</v>
+      </c>
+      <c r="V222" t="n">
+        <v>0</v>
+      </c>
+      <c r="W222" t="n">
+        <v>0</v>
+      </c>
+      <c r="X222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL222" s="3" t="n">
+        <v>45879.875</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45879</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M223" t="n">
         <v>3.25</v>
       </c>
-      <c r="O221" t="n">
-        <v>0</v>
-      </c>
-      <c r="P221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
-      <c r="S221" t="n">
-        <v>0</v>
-      </c>
-      <c r="T221" t="n">
-        <v>0</v>
-      </c>
-      <c r="U221" t="n">
-        <v>0</v>
-      </c>
-      <c r="V221" t="n">
-        <v>0</v>
-      </c>
-      <c r="W221" t="n">
-        <v>0</v>
-      </c>
-      <c r="X221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z221" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA221" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB221" t="n">
+      <c r="N223" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="n">
+        <v>0</v>
+      </c>
+      <c r="T223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="n">
+        <v>0</v>
+      </c>
+      <c r="V223" t="n">
+        <v>0</v>
+      </c>
+      <c r="W223" t="n">
+        <v>0</v>
+      </c>
+      <c r="X223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB223" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC221" t="n">
+      <c r="AC223" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD221" t="n">
+      <c r="AD223" t="n">
         <v>2.47</v>
       </c>
-      <c r="AE221" t="n">
+      <c r="AE223" t="n">
         <v>1.54</v>
       </c>
-      <c r="AF221" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG221" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH221" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI221" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL221" s="3" t="n">
+      <c r="AF223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL223" s="3" t="n">
         <v>45879.95833333334</v>
       </c>
     </row>
